--- a/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
+++ b/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,17 +418,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>served</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>candidate</t>
         </is>
@@ -1540,12 +1528,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>

--- a/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
+++ b/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,17 +430,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>served</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>candidate</t>
         </is>
@@ -1528,12 +1540,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>

--- a/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
+++ b/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,21 +414,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>served</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>candidate</t>
         </is>
@@ -748,7 +736,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>is_home</t>
+          <t>back_to_back_home</t>
         </is>
       </c>
       <c r="B25" t="b">
@@ -761,7 +749,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>event_three_rate_diff</t>
+          <t>back_to_back_away</t>
         </is>
       </c>
       <c r="B26" t="b">
@@ -774,7 +762,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>event_rim_rate_diff</t>
+          <t>ewm_net_points_home</t>
         </is>
       </c>
       <c r="B27" t="b">
@@ -787,7 +775,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>event_live_tov_rate_diff</t>
+          <t>ewm_net_points_away</t>
         </is>
       </c>
       <c r="B28" t="b">
@@ -800,7 +788,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>event_and_in_rate_diff</t>
+          <t>ewm_pace_home</t>
         </is>
       </c>
       <c r="B29" t="b">
@@ -813,7 +801,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>event_shot_distance_diff</t>
+          <t>ewm_pace_away</t>
         </is>
       </c>
       <c r="B30" t="b">
@@ -826,7 +814,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>event_possessions_diff</t>
+          <t>ewm_efg_pct_home</t>
         </is>
       </c>
       <c r="B31" t="b">
@@ -839,7 +827,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>event_shooting_fouls_diff</t>
+          <t>ewm_efg_pct_away</t>
         </is>
       </c>
       <c r="B32" t="b">
@@ -852,7 +840,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>event_q4_points_diff</t>
+          <t>ewm_turnover_margin_home</t>
         </is>
       </c>
       <c r="B33" t="b">
@@ -865,7 +853,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pl_ts_c_away</t>
+          <t>ewm_turnover_margin_away</t>
         </is>
       </c>
       <c r="B34" t="b">
@@ -878,7 +866,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pl_ts_c_home</t>
+          <t>ewm_rebound_margin_home</t>
         </is>
       </c>
       <c r="B35" t="b">
@@ -891,7 +879,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pl_ts_c_diff</t>
+          <t>ewm_rebound_margin_away</t>
         </is>
       </c>
       <c r="B36" t="b">
@@ -904,7 +892,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pl_ts_f_away</t>
+          <t>ewm_ast_per_game_home</t>
         </is>
       </c>
       <c r="B37" t="b">
@@ -917,7 +905,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pl_ts_f_home</t>
+          <t>ewm_ast_per_game_away</t>
         </is>
       </c>
       <c r="B38" t="b">
@@ -930,7 +918,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pl_ts_f_diff</t>
+          <t>event_three_rate_home</t>
         </is>
       </c>
       <c r="B39" t="b">
@@ -943,7 +931,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pl_ts_g_away</t>
+          <t>event_three_rate_away</t>
         </is>
       </c>
       <c r="B40" t="b">
@@ -956,7 +944,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pl_ts_g_home</t>
+          <t>event_rim_rate_home</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -969,7 +957,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pl_ts_g_diff</t>
+          <t>event_rim_rate_away</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -982,397 +970,397 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_ewm_diff</t>
+          <t>event_live_tov_rate_home</t>
         </is>
       </c>
       <c r="B43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_ewm_home</t>
+          <t>event_live_tov_rate_away</t>
         </is>
       </c>
       <c r="B44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_ewm_away</t>
+          <t>event_and_in_rate_home</t>
         </is>
       </c>
       <c r="B45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_roll_diff</t>
+          <t>event_and_in_rate_away</t>
         </is>
       </c>
       <c r="B46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_roll_home</t>
+          <t>event_shot_distance_home</t>
         </is>
       </c>
       <c r="B47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nba_points_for_pg_roll_away</t>
+          <t>event_shot_distance_away</t>
         </is>
       </c>
       <c r="B48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_ewm_diff</t>
+          <t>event_possessions_home</t>
         </is>
       </c>
       <c r="B49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_ewm_home</t>
+          <t>event_possessions_away</t>
         </is>
       </c>
       <c r="B50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_ewm_away</t>
+          <t>event_shooting_fouls_home</t>
         </is>
       </c>
       <c r="B51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_roll_diff</t>
+          <t>event_shooting_fouls_away</t>
         </is>
       </c>
       <c r="B52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_roll_home</t>
+          <t>event_q4_points_home</t>
         </is>
       </c>
       <c r="B53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nba_points_against_pg_roll_away</t>
+          <t>event_q4_points_away</t>
         </is>
       </c>
       <c r="B54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_ewm_diff</t>
+          <t>is_home</t>
         </is>
       </c>
       <c r="B55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_ewm_home</t>
+          <t>event_three_rate_diff</t>
         </is>
       </c>
       <c r="B56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_ewm_away</t>
+          <t>event_rim_rate_diff</t>
         </is>
       </c>
       <c r="B57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_roll_diff</t>
+          <t>event_live_tov_rate_diff</t>
         </is>
       </c>
       <c r="B58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_roll_home</t>
+          <t>event_and_in_rate_diff</t>
         </is>
       </c>
       <c r="B59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nba_assists_per_game_roll_away</t>
+          <t>event_shot_distance_diff</t>
         </is>
       </c>
       <c r="B60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_ewm_diff</t>
+          <t>event_possessions_diff</t>
         </is>
       </c>
       <c r="B61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_ewm_home</t>
+          <t>event_shooting_fouls_diff</t>
         </is>
       </c>
       <c r="B62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_ewm_away</t>
+          <t>event_q4_points_diff</t>
         </is>
       </c>
       <c r="B63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_roll_diff</t>
+          <t>pl_ts_c_away</t>
         </is>
       </c>
       <c r="B64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_roll_home</t>
+          <t>pl_ts_c_home</t>
         </is>
       </c>
       <c r="B65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nba_rebounds_per_game_roll_away</t>
+          <t>pl_ts_c_diff</t>
         </is>
       </c>
       <c r="B66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_ewm_diff</t>
+          <t>pl_ts_f_away</t>
         </is>
       </c>
       <c r="B67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_ewm_home</t>
+          <t>pl_ts_f_home</t>
         </is>
       </c>
       <c r="B68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_ewm_away</t>
+          <t>pl_ts_f_diff</t>
         </is>
       </c>
       <c r="B69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_roll_diff</t>
+          <t>pl_ts_g_away</t>
         </is>
       </c>
       <c r="B70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_roll_home</t>
+          <t>pl_ts_g_home</t>
         </is>
       </c>
       <c r="B71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>nba_turnovers_per_game_roll_away</t>
+          <t>pl_ts_g_diff</t>
         </is>
       </c>
       <c r="B72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_ewm_diff</t>
+          <t>nba_points_for_pg_ewm_diff</t>
         </is>
       </c>
       <c r="B73" t="b">
@@ -1385,7 +1373,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_ewm_home</t>
+          <t>nba_points_for_pg_ewm_home</t>
         </is>
       </c>
       <c r="B74" t="b">
@@ -1398,7 +1386,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_ewm_away</t>
+          <t>nba_points_for_pg_ewm_away</t>
         </is>
       </c>
       <c r="B75" t="b">
@@ -1411,7 +1399,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_roll_diff</t>
+          <t>nba_points_for_pg_roll_diff</t>
         </is>
       </c>
       <c r="B76" t="b">
@@ -1424,7 +1412,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_roll_home</t>
+          <t>nba_points_for_pg_roll_home</t>
         </is>
       </c>
       <c r="B77" t="b">
@@ -1437,7 +1425,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nba_three_point_pct_roll_away</t>
+          <t>nba_points_for_pg_roll_away</t>
         </is>
       </c>
       <c r="B78" t="b">
@@ -1450,7 +1438,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nba_free_throw_pct_ewm_diff</t>
+          <t>nba_points_against_pg_ewm_diff</t>
         </is>
       </c>
       <c r="B79" t="b">
@@ -1463,7 +1451,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nba_free_throw_pct_ewm_home</t>
+          <t>nba_points_against_pg_ewm_home</t>
         </is>
       </c>
       <c r="B80" t="b">
@@ -1476,7 +1464,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nba_free_throw_pct_ewm_away</t>
+          <t>nba_points_against_pg_ewm_away</t>
         </is>
       </c>
       <c r="B81" t="b">
@@ -1489,7 +1477,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nba_free_throw_pct_roll_diff</t>
+          <t>nba_points_against_pg_roll_diff</t>
         </is>
       </c>
       <c r="B82" t="b">
@@ -1502,7 +1490,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nba_free_throw_pct_roll_home</t>
+          <t>nba_points_against_pg_roll_home</t>
         </is>
       </c>
       <c r="B83" t="b">
@@ -1515,13 +1503,403 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>nba_points_against_pg_roll_away</t>
+        </is>
+      </c>
+      <c r="B84" t="b">
+        <v>0</v>
+      </c>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_ewm_diff</t>
+        </is>
+      </c>
+      <c r="B85" t="b">
+        <v>0</v>
+      </c>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_ewm_home</t>
+        </is>
+      </c>
+      <c r="B86" t="b">
+        <v>0</v>
+      </c>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_ewm_away</t>
+        </is>
+      </c>
+      <c r="B87" t="b">
+        <v>0</v>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_roll_diff</t>
+        </is>
+      </c>
+      <c r="B88" t="b">
+        <v>0</v>
+      </c>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_roll_home</t>
+        </is>
+      </c>
+      <c r="B89" t="b">
+        <v>0</v>
+      </c>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>nba_assists_per_game_roll_away</t>
+        </is>
+      </c>
+      <c r="B90" t="b">
+        <v>0</v>
+      </c>
+      <c r="C90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_ewm_diff</t>
+        </is>
+      </c>
+      <c r="B91" t="b">
+        <v>0</v>
+      </c>
+      <c r="C91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_ewm_home</t>
+        </is>
+      </c>
+      <c r="B92" t="b">
+        <v>0</v>
+      </c>
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_ewm_away</t>
+        </is>
+      </c>
+      <c r="B93" t="b">
+        <v>0</v>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_roll_diff</t>
+        </is>
+      </c>
+      <c r="B94" t="b">
+        <v>0</v>
+      </c>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_roll_home</t>
+        </is>
+      </c>
+      <c r="B95" t="b">
+        <v>0</v>
+      </c>
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>nba_rebounds_per_game_roll_away</t>
+        </is>
+      </c>
+      <c r="B96" t="b">
+        <v>0</v>
+      </c>
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_ewm_diff</t>
+        </is>
+      </c>
+      <c r="B97" t="b">
+        <v>0</v>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_ewm_home</t>
+        </is>
+      </c>
+      <c r="B98" t="b">
+        <v>0</v>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_ewm_away</t>
+        </is>
+      </c>
+      <c r="B99" t="b">
+        <v>0</v>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_roll_diff</t>
+        </is>
+      </c>
+      <c r="B100" t="b">
+        <v>0</v>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_roll_home</t>
+        </is>
+      </c>
+      <c r="B101" t="b">
+        <v>0</v>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>nba_turnovers_per_game_roll_away</t>
+        </is>
+      </c>
+      <c r="B102" t="b">
+        <v>0</v>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_ewm_diff</t>
+        </is>
+      </c>
+      <c r="B103" t="b">
+        <v>0</v>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_ewm_home</t>
+        </is>
+      </c>
+      <c r="B104" t="b">
+        <v>0</v>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_ewm_away</t>
+        </is>
+      </c>
+      <c r="B105" t="b">
+        <v>0</v>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_roll_diff</t>
+        </is>
+      </c>
+      <c r="B106" t="b">
+        <v>0</v>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_roll_home</t>
+        </is>
+      </c>
+      <c r="B107" t="b">
+        <v>0</v>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>nba_three_point_pct_roll_away</t>
+        </is>
+      </c>
+      <c r="B108" t="b">
+        <v>0</v>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>nba_free_throw_pct_ewm_diff</t>
+        </is>
+      </c>
+      <c r="B109" t="b">
+        <v>0</v>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>nba_free_throw_pct_ewm_home</t>
+        </is>
+      </c>
+      <c r="B110" t="b">
+        <v>0</v>
+      </c>
+      <c r="C110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>nba_free_throw_pct_ewm_away</t>
+        </is>
+      </c>
+      <c r="B111" t="b">
+        <v>0</v>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>nba_free_throw_pct_roll_diff</t>
+        </is>
+      </c>
+      <c r="B112" t="b">
+        <v>0</v>
+      </c>
+      <c r="C112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>nba_free_throw_pct_roll_home</t>
+        </is>
+      </c>
+      <c r="B113" t="b">
+        <v>0</v>
+      </c>
+      <c r="C113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>nba_free_throw_pct_roll_away</t>
         </is>
       </c>
-      <c r="B84" t="b">
-        <v>0</v>
-      </c>
-      <c r="C84" t="b">
+      <c r="B114" t="b">
+        <v>0</v>
+      </c>
+      <c r="C114" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1540,12 +1918,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -1583,7 +1961,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nba-prod-v2.0-events</t>
+          <t>nba-prod-v2.1-per-side</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1985,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>["elo_diff", "win_pct_diff", "rest_days_diff", "back_to_back_diff", "ewm_net_points_diff", "ewm_off_rating_diff", "ewm_def_rating_diff", "ewm_pace_diff", "ewm_efg_pct_diff", "ewm_turnover_margin_diff", "ewm_rebound_margin_diff", "ewm_ast_per_game_diff", "is_playoffs", "elo_home", "elo_away", "win_pct_home", "win_pct_away", "ewm_off_rating_home", "ewm_off_rating_away", "ewm_def_rating_home", "ewm_def_rating_away", "rest_days_home", "rest_days_away", "is_home", "event_three_rate_diff", "event_rim_rate_diff", "event_live_tov_rate_diff", "event_and_in_rate_diff", "event_shot_distance_diff", "event_possessions_diff", "event_shooting_fouls_diff", "event_q4_points_diff", "pl_ts_c_away", "pl_ts_c_home", "pl_ts_c_diff", "pl_ts_f_away", "pl_ts_f_home", "pl_ts_f_diff", "pl_ts_g_away", "pl_ts_g_home", "pl_ts_g_diff"]</t>
+          <t>["elo_diff", "win_pct_diff", "rest_days_diff", "back_to_back_diff", "ewm_net_points_diff", "ewm_off_rating_diff", "ewm_def_rating_diff", "ewm_pace_diff", "ewm_efg_pct_diff", "ewm_turnover_margin_diff", "ewm_rebound_margin_diff", "ewm_ast_per_game_diff", "is_playoffs", "elo_home", "elo_away", "win_pct_home", "win_pct_away", "ewm_off_rating_home", "ewm_off_rating_away", "ewm_def_rating_home", "ewm_def_rating_away", "rest_days_home", "rest_days_away", "back_to_back_home", "back_to_back_away", "ewm_net_points_home", "ewm_net_points_away", "ewm_pace_home", "ewm_pace_away", "ewm_efg_pct_home", "ewm_efg_pct_away", "ewm_turnover_margin_home", "ewm_turnover_margin_away", "ewm_rebound_margin_home", "ewm_rebound_margin_away", "ewm_ast_per_game_home", "ewm_ast_per_game_away", "event_three_rate_home", "event_three_rate_away", "event_rim_rate_home", "event_rim_rate_away", "event_live_tov_rate_home", "event_live_tov_rate_away", "event_and_in_rate_home", "event_and_in_rate_away", "event_shot_distance_home", "event_shot_distance_away", "event_possessions_home", "event_possessions_away", "event_shooting_fouls_home", "event_shooting_fouls_away", "event_q4_points_home", "event_q4_points_away", "is_home", "event_three_rate_diff", "event_rim_rate_diff", "event_live_tov_rate_diff", "event_and_in_rate_diff", "event_shot_distance_diff", "event_possessions_diff", "event_shooting_fouls_diff", "event_q4_points_diff", "pl_ts_c_away", "pl_ts_c_home", "pl_ts_c_diff", "pl_ts_f_away", "pl_ts_f_home", "pl_ts_f_diff", "pl_ts_g_away", "pl_ts_g_home", "pl_ts_g_diff"]</t>
         </is>
       </c>
     </row>

--- a/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
+++ b/nba-backend/data_delivery/nba_feature_workbook_20260927.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,17 +430,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>served</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>candidate</t>
         </is>
@@ -1918,12 +1930,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
